--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_whitespace.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_whitespace.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>59.82</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C3" t="n">
-        <v>38.5</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>
